--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CONSTRUCCIONES GONZALO CRESPO PAS PIÉLAGOS.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CONSTRUCCIONES GONZALO CRESPO PAS PIÉLAGOS.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. YAILO</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>34.92749999999999</v>
+        <v>41.3871</v>
       </c>
       <c r="E2" t="n">
-        <v>47.625</v>
+        <v>47.8576</v>
       </c>
       <c r="F2" t="n">
-        <v>-12.6975</v>
+        <v>-6.470400000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>42.695</v>
+        <v>-20.379</v>
       </c>
       <c r="H2" t="n">
-        <v>40.8102</v>
+        <v>-11.3705</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8848</v>
+        <v>-9.008500000000002</v>
       </c>
       <c r="J2" t="n">
-        <v>83.6294</v>
+        <v>26.7635</v>
       </c>
       <c r="K2" t="n">
-        <v>68.25490000000001</v>
+        <v>18.1046</v>
       </c>
       <c r="L2" t="n">
-        <v>15.3747</v>
+        <v>8.6587</v>
       </c>
       <c r="M2" t="n">
-        <v>-40.9346</v>
+        <v>-47.1428</v>
       </c>
       <c r="N2" t="n">
-        <v>-27.4449</v>
+        <v>-29.4751</v>
       </c>
       <c r="O2" t="n">
-        <v>-13.4897</v>
+        <v>-17.6676</v>
       </c>
       <c r="P2" t="n">
-        <v>-36.8645</v>
+        <v>38.2158</v>
       </c>
       <c r="Q2" t="n">
-        <v>-89.3626</v>
+        <v>-22.0025</v>
       </c>
       <c r="R2" t="n">
-        <v>52.4983</v>
+        <v>60.2188</v>
       </c>
       <c r="S2" t="n">
-        <v>8.127500000000001</v>
+        <v>-11.7096</v>
       </c>
       <c r="T2" t="n">
-        <v>10.2821</v>
+        <v>-5.8854</v>
       </c>
       <c r="U2" t="n">
-        <v>-2.1544</v>
+        <v>-5.8241</v>
       </c>
       <c r="V2" t="n">
-        <v>20.9695</v>
+        <v>35.26</v>
       </c>
       <c r="W2" t="n">
-        <v>43.0763</v>
+        <v>48.9821</v>
       </c>
       <c r="X2" t="n">
-        <v>-22.1064</v>
+        <v>-13.7224</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>14</v>
       </c>
       <c r="D3" t="n">
-        <v>32.1551</v>
+        <v>27.9899</v>
       </c>
       <c r="E3" t="n">
-        <v>20.4283</v>
+        <v>17.3366</v>
       </c>
       <c r="F3" t="n">
-        <v>11.7267</v>
+        <v>10.6531</v>
       </c>
       <c r="G3" t="n">
         <v>7.3704</v>
@@ -688,13 +688,13 @@
         <v>23.5471</v>
       </c>
       <c r="S3" t="n">
-        <v>8.098800000000001</v>
+        <v>3.9339</v>
       </c>
       <c r="T3" t="n">
-        <v>5.2512</v>
+        <v>2.1598</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8477</v>
+        <v>1.7739</v>
       </c>
       <c r="V3" t="n">
         <v>9.158299999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>A. YAILO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D4" t="n">
-        <v>24.3189</v>
+        <v>25.5081</v>
       </c>
       <c r="E4" t="n">
-        <v>13.5295</v>
+        <v>38.7194</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7891</v>
+        <v>-13.2111</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2696</v>
+        <v>42.695</v>
       </c>
       <c r="H4" t="n">
-        <v>14.554</v>
+        <v>40.8102</v>
       </c>
       <c r="I4" t="n">
-        <v>-13.2849</v>
+        <v>1.8848</v>
       </c>
       <c r="J4" t="n">
-        <v>21.99</v>
+        <v>83.6294</v>
       </c>
       <c r="K4" t="n">
-        <v>30.6586</v>
+        <v>68.25490000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.668200000000001</v>
+        <v>15.3747</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.7206</v>
+        <v>-40.9346</v>
       </c>
       <c r="N4" t="n">
-        <v>-16.1043</v>
+        <v>-27.4449</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.6163</v>
+        <v>-13.4897</v>
       </c>
       <c r="P4" t="n">
-        <v>11.3874</v>
+        <v>-36.8645</v>
       </c>
       <c r="Q4" t="n">
-        <v>-27.5997</v>
+        <v>-89.3626</v>
       </c>
       <c r="R4" t="n">
-        <v>38.9875</v>
+        <v>52.4983</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8433</v>
+        <v>-1.291800000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1171</v>
+        <v>1.3763</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2735999999999997</v>
+        <v>-2.667899999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>9.818800000000001</v>
+        <v>20.9695</v>
       </c>
       <c r="W4" t="n">
-        <v>17.0226</v>
+        <v>43.0763</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.2039</v>
+        <v>-22.1064</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>21.216</v>
+        <v>23.7515</v>
       </c>
       <c r="E5" t="n">
-        <v>38.2806</v>
+        <v>13.4207</v>
       </c>
       <c r="F5" t="n">
-        <v>-17.0644</v>
+        <v>10.3309</v>
       </c>
       <c r="G5" t="n">
-        <v>-20.379</v>
+        <v>1.2696</v>
       </c>
       <c r="H5" t="n">
-        <v>-11.3705</v>
+        <v>14.554</v>
       </c>
       <c r="I5" t="n">
-        <v>-9.008500000000002</v>
+        <v>-13.2849</v>
       </c>
       <c r="J5" t="n">
-        <v>26.7635</v>
+        <v>21.99</v>
       </c>
       <c r="K5" t="n">
-        <v>18.1046</v>
+        <v>30.6586</v>
       </c>
       <c r="L5" t="n">
-        <v>8.6587</v>
+        <v>-8.668200000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-47.1428</v>
+        <v>-20.7206</v>
       </c>
       <c r="N5" t="n">
-        <v>-29.4751</v>
+        <v>-16.1043</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.6676</v>
+        <v>-4.6163</v>
       </c>
       <c r="P5" t="n">
-        <v>38.2158</v>
+        <v>11.3874</v>
       </c>
       <c r="Q5" t="n">
-        <v>-22.0025</v>
+        <v>-27.5997</v>
       </c>
       <c r="R5" t="n">
-        <v>60.2188</v>
+        <v>38.9875</v>
       </c>
       <c r="S5" t="n">
-        <v>-31.8806</v>
+        <v>1.2761</v>
       </c>
       <c r="T5" t="n">
-        <v>-15.4623</v>
+        <v>2.0079</v>
       </c>
       <c r="U5" t="n">
-        <v>-16.4183</v>
+        <v>-0.7321</v>
       </c>
       <c r="V5" t="n">
-        <v>35.26</v>
+        <v>9.818800000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>48.9821</v>
+        <v>17.0226</v>
       </c>
       <c r="X5" t="n">
-        <v>-13.7224</v>
+        <v>-7.2039</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HERNANDO PEREZ</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>8.288600000000001</v>
+        <v>3.287799999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>17.9791</v>
+        <v>18.9972</v>
       </c>
       <c r="F6" t="n">
-        <v>-9.690300000000001</v>
+        <v>-15.7095</v>
       </c>
       <c r="G6" t="n">
-        <v>-8.8902</v>
+        <v>29.5381</v>
       </c>
       <c r="H6" t="n">
-        <v>-4.5045</v>
+        <v>11.229</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.385800000000001</v>
+        <v>18.3088</v>
       </c>
       <c r="J6" t="n">
-        <v>13.4736</v>
+        <v>62.9631</v>
       </c>
       <c r="K6" t="n">
-        <v>8.0868</v>
+        <v>38.8797</v>
       </c>
       <c r="L6" t="n">
-        <v>5.3869</v>
+        <v>24.084</v>
       </c>
       <c r="M6" t="n">
-        <v>-22.3636</v>
+        <v>-33.4252</v>
       </c>
       <c r="N6" t="n">
-        <v>-12.5911</v>
+        <v>-27.6509</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.772400000000001</v>
+        <v>-5.7744</v>
       </c>
       <c r="P6" t="n">
-        <v>5.210999999999999</v>
+        <v>-29.3373</v>
       </c>
       <c r="Q6" t="n">
-        <v>-22.9676</v>
+        <v>-77.00999999999999</v>
       </c>
       <c r="R6" t="n">
-        <v>28.179</v>
+        <v>47.6732</v>
       </c>
       <c r="S6" t="n">
-        <v>11.2309</v>
+        <v>-9.0198</v>
       </c>
       <c r="T6" t="n">
-        <v>13.0338</v>
+        <v>-7.660699999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.8031</v>
+        <v>-1.3593</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7368000000000002</v>
+        <v>12.1067</v>
       </c>
       <c r="W6" t="n">
-        <v>14.4399</v>
+        <v>40.7046</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.7033</v>
+        <v>-28.5978</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0676</v>
+        <v>0.6794999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>1.7384</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.671</v>
+        <v>-0.2171000000000002</v>
       </c>
       <c r="G7" t="n">
         <v>-2.3617</v>
@@ -1000,13 +1000,13 @@
         <v>4.246</v>
       </c>
       <c r="S7" t="n">
-        <v>2.4689</v>
+        <v>2.0808</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1311</v>
+        <v>1.2894</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3377</v>
+        <v>0.7915</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1279</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ MARCILLA</t>
+          <t>M. HERNANDO PEREZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2399</v>
+        <v>0.5185000000000008</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2023</v>
+        <v>9.195399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4421</v>
+        <v>-8.6768</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0101</v>
+        <v>-8.8902</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3737</v>
+        <v>-4.5045</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3838</v>
+        <v>-4.385800000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2326</v>
+        <v>13.4736</v>
       </c>
       <c r="K8" t="n">
-        <v>1.656</v>
+        <v>8.0868</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4234</v>
+        <v>5.3869</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2426</v>
+        <v>-22.3636</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2822</v>
+        <v>-12.5911</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9604000000000001</v>
+        <v>-9.772400000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.772</v>
+        <v>5.210999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9301</v>
+        <v>-22.9676</v>
       </c>
       <c r="R8" t="n">
-        <v>1.158</v>
+        <v>28.179</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1984</v>
+        <v>3.4608</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5559</v>
+        <v>4.2502</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3577</v>
+        <v>-0.7894000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6562</v>
+        <v>0.7368000000000002</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6562</v>
+        <v>14.4399</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-13.7033</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6359</v>
+        <v>-1.5763</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.5146000000000001</v>
+        <v>-0.4552</v>
       </c>
       <c r="F9" t="n">
         <v>-1.1213</v>
@@ -1156,13 +1156,13 @@
         <v>2.123</v>
       </c>
       <c r="S9" t="n">
-        <v>0.267</v>
+        <v>0.3264</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1361</v>
+        <v>-0.07669999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4032</v>
+        <v>0.4031</v>
       </c>
       <c r="V9" t="n">
         <v>-3.6417</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. RIASCOS PEREA</t>
+          <t>D. FERNANDEZ MARCILLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,67 +1186,67 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9855</v>
+        <v>-2.2014</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7735</v>
+        <v>-0.9994000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2119</v>
+        <v>-1.202</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.269</v>
+        <v>-1.0101</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.2562</v>
+        <v>0.3737</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.01289999999999997</v>
+        <v>-1.3838</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.9407</v>
+        <v>1.2326</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.9407</v>
+        <v>1.656</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.4234</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3283</v>
+        <v>-2.2426</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3154</v>
+        <v>-1.2822</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.01289999999999997</v>
+        <v>-0.9604000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.386</v>
+        <v>-0.772</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.579</v>
+        <v>1.158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3305</v>
+        <v>0.237</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1322</v>
+        <v>0.3543</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4627</v>
+        <v>-0.1173</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>A. RUIZ VICENTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.3981</v>
+        <v>-2.273099999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>7.915000000000001</v>
+        <v>-3.0827</v>
       </c>
       <c r="F11" t="n">
-        <v>-14.3133</v>
+        <v>0.8097000000000005</v>
       </c>
       <c r="G11" t="n">
-        <v>29.5381</v>
+        <v>-5.400499999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>11.229</v>
+        <v>-3.9981</v>
       </c>
       <c r="I11" t="n">
-        <v>18.3088</v>
+        <v>-1.402499999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>62.9631</v>
+        <v>20.1054</v>
       </c>
       <c r="K11" t="n">
-        <v>38.8797</v>
+        <v>12.0135</v>
       </c>
       <c r="L11" t="n">
-        <v>24.084</v>
+        <v>8.091699999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>-33.4252</v>
+        <v>-25.5054</v>
       </c>
       <c r="N11" t="n">
-        <v>-27.6509</v>
+        <v>-16.0118</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.7744</v>
+        <v>-9.4939</v>
       </c>
       <c r="P11" t="n">
-        <v>-29.3373</v>
+        <v>7.1414</v>
       </c>
       <c r="Q11" t="n">
-        <v>-77.00999999999999</v>
+        <v>-36.0923</v>
       </c>
       <c r="R11" t="n">
-        <v>47.6732</v>
+        <v>43.2342</v>
       </c>
       <c r="S11" t="n">
-        <v>-18.7053</v>
+        <v>-6.4105</v>
       </c>
       <c r="T11" t="n">
-        <v>-18.7424</v>
+        <v>-3.0068</v>
       </c>
       <c r="U11" t="n">
-        <v>0.03669999999999987</v>
+        <v>-3.4035</v>
       </c>
       <c r="V11" t="n">
-        <v>12.1067</v>
+        <v>2.3968</v>
       </c>
       <c r="W11" t="n">
-        <v>40.7046</v>
+        <v>15.9115</v>
       </c>
       <c r="X11" t="n">
-        <v>-28.5978</v>
+        <v>-13.5149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. RUIZ VICENTE</t>
+          <t>J. RIASCOS PEREA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.382900000000001</v>
+        <v>-4.0004</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.556699999999999</v>
+        <v>-2.8955</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.825899999999999</v>
+        <v>-1.1048</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.400499999999999</v>
+        <v>-3.269</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.9981</v>
+        <v>-3.2562</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.402499999999999</v>
+        <v>-0.01289999999999997</v>
       </c>
       <c r="J12" t="n">
-        <v>20.1054</v>
+        <v>-1.9407</v>
       </c>
       <c r="K12" t="n">
-        <v>12.0135</v>
+        <v>-1.9407</v>
       </c>
       <c r="L12" t="n">
-        <v>8.091699999999999</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-25.5054</v>
+        <v>-1.3283</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.0118</v>
+        <v>-1.3154</v>
       </c>
       <c r="O12" t="n">
-        <v>-9.4939</v>
+        <v>-0.01289999999999997</v>
       </c>
       <c r="P12" t="n">
-        <v>7.1414</v>
+        <v>-0.386</v>
       </c>
       <c r="Q12" t="n">
-        <v>-36.0923</v>
+        <v>-0.965</v>
       </c>
       <c r="R12" t="n">
-        <v>43.2342</v>
+        <v>0.579</v>
       </c>
       <c r="S12" t="n">
-        <v>-13.5205</v>
+        <v>-0.3453</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.481199999999999</v>
+        <v>0.01020000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-7.0392</v>
+        <v>-0.3556</v>
       </c>
       <c r="V12" t="n">
-        <v>2.3968</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>15.9115</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-13.5149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-11.1826</v>
+        <v>-5.392099999999997</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9349</v>
+        <v>-1.878899999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.247600000000001</v>
+        <v>-3.513200000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-14.6029</v>
@@ -1468,13 +1468,13 @@
         <v>46.7083</v>
       </c>
       <c r="S13" t="n">
-        <v>-12.1821</v>
+        <v>-6.3916</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.1232</v>
+        <v>-3.0674</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.0586</v>
+        <v>-3.3244</v>
       </c>
       <c r="V13" t="n">
         <v>4.0217</v>
@@ -1501,13 +1501,13 @@
         <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-12.8064</v>
+        <v>-8.4552</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.2564</v>
+        <v>0.7212999999999996</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.5501</v>
+        <v>-9.176500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>5.8611</v>
@@ -1546,13 +1546,13 @@
         <v>21.617</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.519</v>
+        <v>-4.1675</v>
       </c>
       <c r="T14" t="n">
-        <v>-7.6698</v>
+        <v>-3.692</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.849</v>
+        <v>-0.4757999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2702</v>
@@ -1579,13 +1579,13 @@
         <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>-19.2007</v>
+        <v>-18.8505</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.3849</v>
+        <v>-11.0511</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.815999999999999</v>
+        <v>-7.7995</v>
       </c>
       <c r="G15" t="n">
         <v>-6.025700000000001</v>
@@ -1624,13 +1624,13 @@
         <v>19.1075</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2949</v>
+        <v>-1.9447</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6913000000000004</v>
+        <v>-1.3577</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6036</v>
+        <v>-0.5873</v>
       </c>
       <c r="V15" t="n">
         <v>-13.5825</v>
@@ -1657,13 +1657,13 @@
         <v>21</v>
       </c>
       <c r="D16" t="n">
-        <v>-39.6073</v>
+        <v>-36.144</v>
       </c>
       <c r="E16" t="n">
-        <v>-16.8402</v>
+        <v>-14.3398</v>
       </c>
       <c r="F16" t="n">
-        <v>-22.7672</v>
+        <v>-21.8045</v>
       </c>
       <c r="G16" t="n">
         <v>-30.4321</v>
@@ -1702,13 +1702,13 @@
         <v>13.5102</v>
       </c>
       <c r="S16" t="n">
-        <v>-4.2601</v>
+        <v>-0.7968999999999998</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.9849</v>
+        <v>-0.4841</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2754</v>
+        <v>-0.3124</v>
       </c>
       <c r="V16" t="n">
         <v>-10.5125</v>
@@ -1735,19 +1735,19 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>16.53439999999997</v>
+        <v>44.22939999999998</v>
       </c>
       <c r="E17" t="n">
-        <v>101.437</v>
+        <v>112.4423</v>
       </c>
       <c r="F17" t="n">
-        <v>-84.9028</v>
+        <v>-68.21299999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.021399999999996</v>
+        <v>-6.021400000000003</v>
       </c>
       <c r="H17" t="n">
-        <v>33.2774</v>
+        <v>33.27740000000001</v>
       </c>
       <c r="I17" t="n">
         <v>-39.2998</v>
@@ -1780,16 +1780,16 @@
         <v>403.3871</v>
       </c>
       <c r="S17" t="n">
-        <v>-58.4582</v>
+        <v>-30.76270000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-24.7878</v>
+        <v>-13.7827</v>
       </c>
       <c r="U17" t="n">
-        <v>-33.67029999999999</v>
+        <v>-16.9806</v>
       </c>
       <c r="V17" t="n">
-        <v>62.67760000000001</v>
+        <v>62.67759999999998</v>
       </c>
       <c r="W17" t="n">
         <v>222.3461</v>
